--- a/Tecnologie/Modulo 1/complementoADue.xlsx
+++ b/Tecnologie/Modulo 1/complementoADue.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24527"/>
-  <workbookPr defaultThemeVersion="166925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24527"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Paolo\Desktop\scuola\Tecnologie\Modulo 1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Paolo\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5AD7588-DA0B-44D7-A6AA-A73FFCD49CCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECFDDC26-EA04-4A5F-9EE7-C895A75ECB2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11295" xr2:uid="{326E5CA0-4302-4B57-BC54-1BC617E5805B}"/>
+    <workbookView xWindow="6720" yWindow="1995" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,31 +34,31 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
-  <si>
-    <t>Numero da convertire</t>
-  </si>
-  <si>
-    <t>numero bit necessari</t>
-  </si>
-  <si>
-    <t>numero senza segno</t>
-  </si>
-  <si>
-    <t>complemento a uno</t>
-  </si>
-  <si>
-    <t>complemento a due</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+  <si>
+    <t>Numero da Convertire</t>
+  </si>
+  <si>
+    <t>Numero di bit necessari</t>
+  </si>
+  <si>
+    <t>Numero senza segno</t>
+  </si>
+  <si>
+    <t>Complemento a 1</t>
+  </si>
+  <si>
+    <t>Complemento a 2</t>
+  </si>
+  <si>
+    <t>Nota: questi due valori sono da inserire in input</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="169" formatCode="000"/>
-  </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -66,16 +66,30 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -83,16 +97,49 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -127,7 +174,7 @@
         <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent1>
       <a:accent2>
         <a:srgbClr val="ED7D31"/>
@@ -139,7 +186,7 @@
         <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent5>
       <a:accent6>
         <a:srgbClr val="70AD47"/>
@@ -186,23 +233,6 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri" panose="020F0502020204030204"/>
@@ -238,23 +268,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -406,30 +419,30 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB64B541-B45E-45EA-BDCB-972E98420956}">
-  <dimension ref="A1:E2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="19" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="16.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
     </row>
@@ -438,12 +451,35 @@
         <v>-3</v>
       </c>
       <c r="B2" s="1">
-        <f>2</f>
-        <v>2</v>
-      </c>
-      <c r="C2" s="2"/>
+        <v>3</v>
+      </c>
+      <c r="C2" s="1" t="str">
+        <f>DEC2BIN(SQRT(A2^2), B2)</f>
+        <v>011</v>
+      </c>
+      <c r="D2" s="3">
+        <f>DEC2BIN((2^B2)-1, B2)-C2</f>
+        <v>100</v>
+      </c>
+      <c r="E2" s="1" t="str">
+        <f>DEC2BIN(BIN2DEC(D2)+1,B2)</f>
+        <v>101</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="4"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="5"/>
+      <c r="B4" s="5"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A3:B4"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/Tecnologie/Modulo 1/complementoADue.xlsx
+++ b/Tecnologie/Modulo 1/complementoADue.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Paolo\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Paolo\Desktop\scuola\Tecnologie\Modulo 1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECFDDC26-EA04-4A5F-9EE7-C895A75ECB2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0601746-D5A3-4D8E-9F4E-61405BF7E42F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6720" yWindow="1995" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>Numero da Convertire</t>
   </si>
@@ -52,6 +52,9 @@
   </si>
   <si>
     <t>Nota: questi due valori sono da inserire in input</t>
+  </si>
+  <si>
+    <t>Numero convertito finale</t>
   </si>
 </sst>
 </file>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -134,6 +137,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -420,16 +424,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="22.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="19.7109375" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="23.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -446,40 +451,59 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
-        <v>-3</v>
+        <f>93</f>
+        <v>93</v>
       </c>
       <c r="B2" s="1">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C2" s="1" t="str">
         <f>DEC2BIN(SQRT(A2^2), B2)</f>
-        <v>011</v>
-      </c>
-      <c r="D2" s="3">
-        <f>DEC2BIN((2^B2)-1, B2)-C2</f>
-        <v>100</v>
+        <v>01011101</v>
+      </c>
+      <c r="D2" s="3" t="str">
+        <f>IF(A2&gt;-1,"//",DEC2BIN((2^B2)-1, B2)-C2)</f>
+        <v>//</v>
       </c>
       <c r="E2" s="1" t="str">
-        <f>DEC2BIN(BIN2DEC(D2)+1,B2)</f>
-        <v>101</v>
+        <f>IF(A2&gt;-1,"//",DEC2BIN(BIN2DEC(D2)+1,B2))</f>
+        <v>//</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="4"/>
+      <c r="B3" s="5"/>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="5"/>
-      <c r="B4" s="5"/>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="6"/>
+      <c r="B4" s="6"/>
+      <c r="G4" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G5" s="4" t="str">
+        <f>IF(A2&gt;-1,C2,E2)</f>
+        <v>01011101</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A3:B4"/>
   </mergeCells>
+  <dataValidations count="2">
+    <dataValidation type="custom" showInputMessage="1" showErrorMessage="1" errorTitle="Numero di bit troppo piccolo!" sqref="B2" xr:uid="{2E940E19-60DB-48EF-B170-2EA4B75F795C}">
+      <formula1>2^B2&gt;SQRT(A2^2)</formula1>
+    </dataValidation>
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2" xr:uid="{45F72298-7CC3-4E38-8138-A66D05A38C59}">
+      <formula1>((2^B2)-1)*-1</formula1>
+      <formula2>(2^B2)-1</formula2>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
